--- a/experiment/template/experiment_configurations.xlsx
+++ b/experiment/template/experiment_configurations.xlsx
@@ -1,19 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nborders/Dropbox/eVOLVER/dpu/experiment/antibiotic_evolution_241127/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nb\Dropbox\PC\Desktop\share\git\photo-stepped-dpu\photo-dpu\experiment\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCC734AF-D5E6-9C44-B7DF-C8A7B461D345}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{557FD0ED-339C-4595-8746-0D9257630E9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="23240" windowHeight="14000" xr2:uid="{AF0A681E-4FC9-47B3-B0CB-C8A6E2C1048C}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13992" tabRatio="696" xr2:uid="{AF0A681E-4FC9-47B3-B0CB-C8A6E2C1048C}"/>
   </bookViews>
   <sheets>
-    <sheet name="light" sheetId="1" r:id="rId1"/>
+    <sheet name="light-control" sheetId="6" r:id="rId1"/>
+    <sheet name="light-step_generation" sheetId="7" r:id="rId2"/>
+    <sheet name="light-steps" sheetId="8" r:id="rId3"/>
+    <sheet name="selection-control" sheetId="3" r:id="rId4"/>
+    <sheet name="selection-step_generation" sheetId="5" r:id="rId5"/>
+    <sheet name="selection-steps" sheetId="2" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,16 +40,550 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>nb</author>
+  </authors>
+  <commentList>
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{2BCF1934-CA14-4558-8F85-4CB590F9F593}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Case insensitive. AUTO if you want to automatically calculate steps; MANUAL if you want to manually input each step; OFF to not do selection</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{F58819B9-C92B-4EC1-9ACA-C767104E6FC1}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>chemical: using a chemical selection. Slow pumps will be used to adjust chemical concentration
+non-chemical: anything that does not require fluidics</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{9C1FFA0F-C589-4DF6-BD3C-F00D1F8EC101}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>number of growth curves required at start of experiment before beginning selection</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{CE48E9CF-7077-430B-9B59-A6F092523145}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>number of growth curves to wait before increasing selection</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{1E770DA1-9A12-4593-80A1-0C9EB8A4C8C3}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>hours; minimum time to spend on a step before increasing or decreasing selection; a reasonable value is at least one full doubling</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{1D231594-1049-4CF2-B10D-FD3A2CC477F2}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>hours; if growth rate measurement is stalled for this many hours, selection pressure will be eased</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{205A5424-FF13-4B0C-B570-43EE36763E36}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>growth rate which triggers increase in selection; for example, if growth rate is 0.1, consider making the max_growthrate 0.06</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0" shapeId="0" xr:uid="{DBF36FF0-8FCC-441F-9221-B34ED36C94B6}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>lowest growth rate allowable for selection; if growth rate is less than this, selection pressure will be eased</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M1" authorId="0" shapeId="0" xr:uid="{8BA85BFB-8CAE-4A9A-86E7-3E79C9464074}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>mostly for logging purposes</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>nb</author>
+  </authors>
+  <commentList>
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{54D46B95-AB0A-4C48-A1A9-CEA405C4AA92}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>True if you want logarithmic steps; False if linear</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{6D39FB04-8740-4B67-A513-842447D2835C}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>first step value. Goes to 0 if we are decreasing selection further</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{265D91C9-519F-4BC8-BCCE-E33369B9E967}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>maximum value your selection can go to; for chemical selection = proportion of stock concentration (don't want to use all of stock)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{F4A56541-F588-44EB-B571-33FBE6EC4947}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>number of steps between min_selection and max_selection</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>nb</author>
+  </authors>
+  <commentList>
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{F64EB04C-D238-4D0D-B7BA-D67E402809FF}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>for manual setting of steps. Should be a comma separated list ie 
+0.1,0.2,0.5,0.75,1</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>nb</author>
+  </authors>
+  <commentList>
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{C06F9245-8FF8-49AE-B4C8-449719000C1A}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Case insensitive. AUTO if you want to automatically calculate steps; MANUAL if you want to manually input each step; OFF to not do selection</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{EE95CE7B-1B53-4764-B91A-3EA95F1200B3}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>chemical: using a chemical selection. Slow pumps will be used to adjust chemical concentration
+non-chemical: anything that does not require fluidics</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{63DEB4E8-EB73-439A-BC9B-98194E237881}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>stock concentrations for each vial; should be low enough that minimum selection level is possible given min_bolus_s</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{C70218A6-8950-4FAE-978C-AC447FD968C7}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>number of growth curves required at start of experiment before beginning selection</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{66FAE453-068B-4933-A0A6-6A71E935D7C6}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>number of growth curves to wait before increasing selection</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{028F0605-8E5D-4C20-811E-5A2E01F240A4}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>hours; minimum time to spend on a step before increasing or decreasing selection; a reasonable value is at least one full doubling</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{E36F93DF-EBE8-44D1-AF93-062AA8622028}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>hours; if growth rate measurement is stalled for this many hours, selection pressure will be eased</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{7473487C-EAD0-4619-B744-412D2C5EC02E}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>growth rate which triggers increase in selection; for example, if growth rate is 0.1, consider making the max_growthrate 0.06</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{2CBD995A-BE07-4274-980F-D6F88C704C98}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>lowest growth rate allowable for selection; if growth rate is less than this, selection pressure will be eased</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{344A0881-BD8B-4858-8DEB-95058FAFC86E}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Number of times to decrease selection chemical concentration to rescue cells by diluting to the last step if selection is too harsh (up to 20 seconds of dilution)
+Set to 0 allow to equilibrate to lower selection concentration over multiple dilutions</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0" shapeId="0" xr:uid="{CA271D26-FA8F-49F9-B5DB-55713FC402EB}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>ratio of the lower_thresh OD below which we will not dilute to rescue; ie if lower_thresh = 2 and rescue_threshold = 0.5, we will not dilute if OD &lt; 1</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M1" authorId="0" shapeId="0" xr:uid="{9BDA1110-A0F3-4860-AAF6-E4BC1B99B5CA}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>mostly for logging purposes</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>nb</author>
+  </authors>
+  <commentList>
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{D5870C89-53E9-4679-868A-0B5598AEF687}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>True if you want logarithmic steps; False if linear</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{08C7C17D-5436-4AAF-A984-1C336350013C}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>first step value. Goes to 0 if we are decreasing selection further</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{B92EB565-D5A1-4176-9EAE-BADFEF07CD27}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>maximum value your selection can go to; for chemical selection = proportion of stock concentration (don't want to use all of stock)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{AE532637-120F-4A36-A815-8735EFD7B470}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>number of steps between min_selection and max_selection</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>nb</author>
+  </authors>
+  <commentList>
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{F94E4579-BB5A-4F48-88E4-B0D04B2AE19E}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>for manual setting of steps. Should be a comma separated list ie 
+0.1,0.2,0.5,0.75,1</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="30">
   <si>
     <t>vial</t>
   </si>
   <si>
-    <t>ON_length</t>
+    <t>steps</t>
   </si>
   <si>
-    <t>OFF_length</t>
+    <t>curves_to_start</t>
+  </si>
+  <si>
+    <t>min_curves_per_step</t>
+  </si>
+  <si>
+    <t>min_step_time</t>
+  </si>
+  <si>
+    <t>growth_stalled_time</t>
+  </si>
+  <si>
+    <t>max_growthrate</t>
+  </si>
+  <si>
+    <t>min_growthrate</t>
+  </si>
+  <si>
+    <t>selection_units</t>
+  </si>
+  <si>
+    <t>ug/mL</t>
+  </si>
+  <si>
+    <t>rescue_dilutions</t>
+  </si>
+  <si>
+    <t>rescue_threshold</t>
+  </si>
+  <si>
+    <t>step_number</t>
+  </si>
+  <si>
+    <t>min_selection</t>
+  </si>
+  <si>
+    <t>max_selection</t>
+  </si>
+  <si>
+    <t>logarithmic_steps</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>1,2,3,4</t>
+  </si>
+  <si>
+    <t>stock_concentration</t>
+  </si>
+  <si>
+    <t>AUTO</t>
+  </si>
+  <si>
+    <t>MANUAL</t>
+  </si>
+  <si>
+    <t>OFF</t>
+  </si>
+  <si>
+    <t>step_type</t>
+  </si>
+  <si>
+    <t>selection_type</t>
+  </si>
+  <si>
+    <t>chemical</t>
   </si>
   <si>
     <t>acclimation_time</t>
@@ -56,14 +595,17 @@
     <t>final_light</t>
   </si>
   <si>
-    <t>cycle_start</t>
+    <t>non-chemical</t>
+  </si>
+  <si>
+    <t>µE per m^2 per s</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -79,13 +621,31 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -100,8 +660,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -436,43 +998,68 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6181C93-C0C9-4D98-99D6-30C9D45B84C6}">
-  <dimension ref="A1:G17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3E53616-8B18-4B6B-A0D4-3486EFA5346E}">
+  <dimension ref="A1:M17"/>
+  <sheetFormatPr defaultColWidth="8.83984375" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="7.83203125" customWidth="1"/>
-    <col min="2" max="2" width="14.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.83984375" customWidth="1"/>
+    <col min="2" max="2" width="14.20703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.1015625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.20703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.15625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.9453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.47265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.15625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.05078125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.3671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.83984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.15625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.62890625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2">
+      <c r="H1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="3">
         <v>0</v>
       </c>
       <c r="B2">
@@ -482,20 +1069,38 @@
         <v>100</v>
       </c>
       <c r="D2">
-        <v>1000</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>24</v>
+        <v>250</v>
+      </c>
+      <c r="E2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" t="s">
+        <v>28</v>
       </c>
       <c r="G2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3">
+        <v>5</v>
+      </c>
+      <c r="H2">
+        <v>5</v>
+      </c>
+      <c r="I2">
+        <v>7</v>
+      </c>
+      <c r="J2">
+        <v>6</v>
+      </c>
+      <c r="K2">
+        <v>0.08</v>
+      </c>
+      <c r="L2">
+        <v>0.1</v>
+      </c>
+      <c r="M2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="3">
         <v>1</v>
       </c>
       <c r="B3">
@@ -505,20 +1110,38 @@
         <v>100</v>
       </c>
       <c r="D3">
-        <v>1000</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3">
-        <v>24</v>
+        <v>250</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
+        <v>28</v>
       </c>
       <c r="G3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4">
+        <v>5</v>
+      </c>
+      <c r="H3">
+        <v>5</v>
+      </c>
+      <c r="I3">
+        <v>7</v>
+      </c>
+      <c r="J3">
+        <v>6</v>
+      </c>
+      <c r="K3">
+        <v>0.08</v>
+      </c>
+      <c r="L3">
+        <v>0.1</v>
+      </c>
+      <c r="M3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="3">
         <v>2</v>
       </c>
       <c r="B4">
@@ -528,20 +1151,38 @@
         <v>100</v>
       </c>
       <c r="D4">
-        <v>1000</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <v>24</v>
+        <v>250</v>
+      </c>
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" t="s">
+        <v>28</v>
       </c>
       <c r="G4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5">
+        <v>5</v>
+      </c>
+      <c r="H4">
+        <v>5</v>
+      </c>
+      <c r="I4">
+        <v>7</v>
+      </c>
+      <c r="J4">
+        <v>6</v>
+      </c>
+      <c r="K4">
+        <v>0.08</v>
+      </c>
+      <c r="L4">
+        <v>0.1</v>
+      </c>
+      <c r="M4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="3">
         <v>3</v>
       </c>
       <c r="B5">
@@ -551,20 +1192,38 @@
         <v>100</v>
       </c>
       <c r="D5">
-        <v>1000</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>24</v>
+        <v>250</v>
+      </c>
+      <c r="E5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" t="s">
+        <v>28</v>
       </c>
       <c r="G5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="H5">
+        <v>5</v>
+      </c>
+      <c r="I5">
+        <v>7</v>
+      </c>
+      <c r="J5">
+        <v>6</v>
+      </c>
+      <c r="K5">
+        <v>0.08</v>
+      </c>
+      <c r="L5">
+        <v>0.1</v>
+      </c>
+      <c r="M5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="3">
         <v>4</v>
       </c>
       <c r="B6">
@@ -574,20 +1233,38 @@
         <v>100</v>
       </c>
       <c r="D6">
-        <v>1000</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>24</v>
+        <v>250</v>
+      </c>
+      <c r="E6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" t="s">
+        <v>28</v>
       </c>
       <c r="G6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="H6">
+        <v>5</v>
+      </c>
+      <c r="I6">
+        <v>7</v>
+      </c>
+      <c r="J6">
+        <v>6</v>
+      </c>
+      <c r="K6">
+        <v>0.08</v>
+      </c>
+      <c r="L6">
+        <v>0.1</v>
+      </c>
+      <c r="M6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="3">
         <v>5</v>
       </c>
       <c r="B7">
@@ -597,20 +1274,38 @@
         <v>100</v>
       </c>
       <c r="D7">
-        <v>1000</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>24</v>
+        <v>250</v>
+      </c>
+      <c r="E7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" t="s">
+        <v>28</v>
       </c>
       <c r="G7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8">
+        <v>5</v>
+      </c>
+      <c r="H7">
+        <v>5</v>
+      </c>
+      <c r="I7">
+        <v>7</v>
+      </c>
+      <c r="J7">
+        <v>6</v>
+      </c>
+      <c r="K7">
+        <v>0.08</v>
+      </c>
+      <c r="L7">
+        <v>0.1</v>
+      </c>
+      <c r="M7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="3">
         <v>6</v>
       </c>
       <c r="B8">
@@ -620,20 +1315,38 @@
         <v>100</v>
       </c>
       <c r="D8">
-        <v>1000</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>24</v>
+        <v>250</v>
+      </c>
+      <c r="E8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" t="s">
+        <v>28</v>
       </c>
       <c r="G8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9">
+        <v>5</v>
+      </c>
+      <c r="H8">
+        <v>5</v>
+      </c>
+      <c r="I8">
+        <v>7</v>
+      </c>
+      <c r="J8">
+        <v>6</v>
+      </c>
+      <c r="K8">
+        <v>0.08</v>
+      </c>
+      <c r="L8">
+        <v>0.1</v>
+      </c>
+      <c r="M8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="3">
         <v>7</v>
       </c>
       <c r="B9">
@@ -643,20 +1356,38 @@
         <v>100</v>
       </c>
       <c r="D9">
-        <v>1000</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>24</v>
+        <v>250</v>
+      </c>
+      <c r="E9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" t="s">
+        <v>28</v>
       </c>
       <c r="G9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10">
+        <v>5</v>
+      </c>
+      <c r="H9">
+        <v>5</v>
+      </c>
+      <c r="I9">
+        <v>7</v>
+      </c>
+      <c r="J9">
+        <v>6</v>
+      </c>
+      <c r="K9">
+        <v>0.08</v>
+      </c>
+      <c r="L9">
+        <v>0.1</v>
+      </c>
+      <c r="M9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="3">
         <v>8</v>
       </c>
       <c r="B10">
@@ -666,20 +1397,38 @@
         <v>100</v>
       </c>
       <c r="D10">
-        <v>1000</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>24</v>
+        <v>250</v>
+      </c>
+      <c r="E10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" t="s">
+        <v>28</v>
       </c>
       <c r="G10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11">
+        <v>5</v>
+      </c>
+      <c r="H10">
+        <v>5</v>
+      </c>
+      <c r="I10">
+        <v>7</v>
+      </c>
+      <c r="J10">
+        <v>6</v>
+      </c>
+      <c r="K10">
+        <v>0.08</v>
+      </c>
+      <c r="L10">
+        <v>0.1</v>
+      </c>
+      <c r="M10" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="3">
         <v>9</v>
       </c>
       <c r="B11">
@@ -689,20 +1438,38 @@
         <v>100</v>
       </c>
       <c r="D11">
-        <v>1000</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>24</v>
+        <v>250</v>
+      </c>
+      <c r="E11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" t="s">
+        <v>28</v>
       </c>
       <c r="G11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12">
+        <v>5</v>
+      </c>
+      <c r="H11">
+        <v>5</v>
+      </c>
+      <c r="I11">
+        <v>7</v>
+      </c>
+      <c r="J11">
+        <v>6</v>
+      </c>
+      <c r="K11">
+        <v>0.08</v>
+      </c>
+      <c r="L11">
+        <v>0.1</v>
+      </c>
+      <c r="M11" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="3">
         <v>10</v>
       </c>
       <c r="B12">
@@ -712,20 +1479,38 @@
         <v>100</v>
       </c>
       <c r="D12">
-        <v>1000</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-      <c r="F12">
-        <v>24</v>
+        <v>250</v>
+      </c>
+      <c r="E12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" t="s">
+        <v>28</v>
       </c>
       <c r="G12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13">
+        <v>5</v>
+      </c>
+      <c r="H12">
+        <v>5</v>
+      </c>
+      <c r="I12">
+        <v>7</v>
+      </c>
+      <c r="J12">
+        <v>6</v>
+      </c>
+      <c r="K12">
+        <v>0.08</v>
+      </c>
+      <c r="L12">
+        <v>0.1</v>
+      </c>
+      <c r="M12" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="3">
         <v>11</v>
       </c>
       <c r="B13">
@@ -735,20 +1520,38 @@
         <v>100</v>
       </c>
       <c r="D13">
-        <v>1000</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>24</v>
+        <v>250</v>
+      </c>
+      <c r="E13" t="s">
+        <v>19</v>
+      </c>
+      <c r="F13" t="s">
+        <v>28</v>
       </c>
       <c r="G13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14">
+        <v>5</v>
+      </c>
+      <c r="H13">
+        <v>5</v>
+      </c>
+      <c r="I13">
+        <v>7</v>
+      </c>
+      <c r="J13">
+        <v>6</v>
+      </c>
+      <c r="K13">
+        <v>0.08</v>
+      </c>
+      <c r="L13">
+        <v>0.1</v>
+      </c>
+      <c r="M13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="3">
         <v>12</v>
       </c>
       <c r="B14">
@@ -758,20 +1561,38 @@
         <v>100</v>
       </c>
       <c r="D14">
-        <v>1000</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-      <c r="F14">
-        <v>24</v>
+        <v>250</v>
+      </c>
+      <c r="E14" t="s">
+        <v>19</v>
+      </c>
+      <c r="F14" t="s">
+        <v>28</v>
       </c>
       <c r="G14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A15">
+        <v>5</v>
+      </c>
+      <c r="H14">
+        <v>5</v>
+      </c>
+      <c r="I14">
+        <v>7</v>
+      </c>
+      <c r="J14">
+        <v>6</v>
+      </c>
+      <c r="K14">
+        <v>0.08</v>
+      </c>
+      <c r="L14">
+        <v>0.1</v>
+      </c>
+      <c r="M14" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="3">
         <v>13</v>
       </c>
       <c r="B15">
@@ -781,20 +1602,38 @@
         <v>100</v>
       </c>
       <c r="D15">
-        <v>1000</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15">
-        <v>24</v>
+        <v>250</v>
+      </c>
+      <c r="E15" t="s">
+        <v>19</v>
+      </c>
+      <c r="F15" t="s">
+        <v>28</v>
       </c>
       <c r="G15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A16">
+        <v>5</v>
+      </c>
+      <c r="H15">
+        <v>5</v>
+      </c>
+      <c r="I15">
+        <v>7</v>
+      </c>
+      <c r="J15">
+        <v>6</v>
+      </c>
+      <c r="K15">
+        <v>0.08</v>
+      </c>
+      <c r="L15">
+        <v>0.1</v>
+      </c>
+      <c r="M15" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="3">
         <v>14</v>
       </c>
       <c r="B16">
@@ -804,20 +1643,38 @@
         <v>100</v>
       </c>
       <c r="D16">
-        <v>1000</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16">
-        <v>24</v>
+        <v>250</v>
+      </c>
+      <c r="E16" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" t="s">
+        <v>28</v>
       </c>
       <c r="G16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17">
+        <v>5</v>
+      </c>
+      <c r="H16">
+        <v>5</v>
+      </c>
+      <c r="I16">
+        <v>7</v>
+      </c>
+      <c r="J16">
+        <v>6</v>
+      </c>
+      <c r="K16">
+        <v>0.08</v>
+      </c>
+      <c r="L16">
+        <v>0.1</v>
+      </c>
+      <c r="M16" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="3">
         <v>15</v>
       </c>
       <c r="B17">
@@ -827,41 +1684,39 @@
         <v>100</v>
       </c>
       <c r="D17">
-        <v>1000</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-      <c r="F17">
-        <v>24</v>
+        <v>250</v>
+      </c>
+      <c r="E17" t="s">
+        <v>19</v>
+      </c>
+      <c r="F17" t="s">
+        <v>28</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="H17">
+        <v>5</v>
+      </c>
+      <c r="I17">
+        <v>7</v>
+      </c>
+      <c r="J17">
+        <v>6</v>
+      </c>
+      <c r="K17">
+        <v>0.08</v>
+      </c>
+      <c r="L17">
+        <v>0.1</v>
+      </c>
+      <c r="M17" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D2:D17">
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F2:F17">
-    <cfRule type="colorScale" priority="3">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G17">
-    <cfRule type="colorScale" priority="1">
+    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -872,5 +1727,1638 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90EEE307-979B-4ECB-9856-D032F4306756}">
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="2" max="2" width="13.68359375" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="12.7890625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.26171875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="b">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>1000</v>
+      </c>
+      <c r="D2">
+        <v>3000</v>
+      </c>
+      <c r="E2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>1000</v>
+      </c>
+      <c r="D3">
+        <v>3000</v>
+      </c>
+      <c r="E3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="b">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>1000</v>
+      </c>
+      <c r="D4">
+        <v>3000</v>
+      </c>
+      <c r="E4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="b">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>1000</v>
+      </c>
+      <c r="D5">
+        <v>3000</v>
+      </c>
+      <c r="E5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="b">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>1000</v>
+      </c>
+      <c r="D6">
+        <v>3000</v>
+      </c>
+      <c r="E6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>1000</v>
+      </c>
+      <c r="D7">
+        <v>3000</v>
+      </c>
+      <c r="E7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" t="b">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>1000</v>
+      </c>
+      <c r="D8">
+        <v>3000</v>
+      </c>
+      <c r="E8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <v>1000</v>
+      </c>
+      <c r="D9">
+        <v>3000</v>
+      </c>
+      <c r="E9">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" t="b">
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <v>1000</v>
+      </c>
+      <c r="D10">
+        <v>3000</v>
+      </c>
+      <c r="E10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11" t="b">
+        <v>0</v>
+      </c>
+      <c r="C11">
+        <v>1000</v>
+      </c>
+      <c r="D11">
+        <v>3000</v>
+      </c>
+      <c r="E11">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12" t="b">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>1000</v>
+      </c>
+      <c r="D12">
+        <v>3000</v>
+      </c>
+      <c r="E12">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13" t="b">
+        <v>1</v>
+      </c>
+      <c r="C13">
+        <v>1000</v>
+      </c>
+      <c r="D13">
+        <v>3000</v>
+      </c>
+      <c r="E13">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14" t="b">
+        <v>1</v>
+      </c>
+      <c r="C14">
+        <v>1000</v>
+      </c>
+      <c r="D14">
+        <v>3000</v>
+      </c>
+      <c r="E14">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15" t="b">
+        <v>1</v>
+      </c>
+      <c r="C15">
+        <v>1000</v>
+      </c>
+      <c r="D15">
+        <v>3000</v>
+      </c>
+      <c r="E15">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16" t="b">
+        <v>0</v>
+      </c>
+      <c r="C16">
+        <v>1000</v>
+      </c>
+      <c r="D16">
+        <v>3000</v>
+      </c>
+      <c r="E16">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17" t="b">
+        <v>0</v>
+      </c>
+      <c r="C17">
+        <v>1000</v>
+      </c>
+      <c r="D17">
+        <v>3000</v>
+      </c>
+      <c r="E17">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31BF5B37-6521-4A27-9828-21E1EAB4E07C}">
+  <dimension ref="A1:B17"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="2" max="2" width="12.89453125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A245ECA0-28EC-4A16-B4DE-14A4BDF7F5DD}">
+  <dimension ref="A1:M17"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="2" max="2" width="13.20703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.20703125" customWidth="1"/>
+    <col min="4" max="4" width="17.68359375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.47265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.1015625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.05078125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.3671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.83984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.15625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.5234375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.20703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.47265625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2">
+        <v>40</v>
+      </c>
+      <c r="E2">
+        <v>5</v>
+      </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>7</v>
+      </c>
+      <c r="H2">
+        <v>6</v>
+      </c>
+      <c r="I2">
+        <v>0.1</v>
+      </c>
+      <c r="J2">
+        <v>0.12</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>0.5</v>
+      </c>
+      <c r="M2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3">
+        <v>40</v>
+      </c>
+      <c r="E3">
+        <v>5</v>
+      </c>
+      <c r="F3">
+        <v>5</v>
+      </c>
+      <c r="G3">
+        <v>7</v>
+      </c>
+      <c r="H3">
+        <v>6</v>
+      </c>
+      <c r="I3">
+        <v>0.1</v>
+      </c>
+      <c r="J3">
+        <v>0.12</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>0.5</v>
+      </c>
+      <c r="M3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4">
+        <v>40</v>
+      </c>
+      <c r="E4">
+        <v>5</v>
+      </c>
+      <c r="F4">
+        <v>5</v>
+      </c>
+      <c r="G4">
+        <v>7</v>
+      </c>
+      <c r="H4">
+        <v>6</v>
+      </c>
+      <c r="I4">
+        <v>0.1</v>
+      </c>
+      <c r="J4">
+        <v>0.12</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="L4">
+        <v>0.5</v>
+      </c>
+      <c r="M4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5">
+        <v>40</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>5</v>
+      </c>
+      <c r="G5">
+        <v>7</v>
+      </c>
+      <c r="H5">
+        <v>6</v>
+      </c>
+      <c r="I5">
+        <v>0.1</v>
+      </c>
+      <c r="J5">
+        <v>0.12</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+      <c r="L5">
+        <v>0.5</v>
+      </c>
+      <c r="M5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6">
+        <v>40</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>5</v>
+      </c>
+      <c r="G6">
+        <v>7</v>
+      </c>
+      <c r="H6">
+        <v>6</v>
+      </c>
+      <c r="I6">
+        <v>0.1</v>
+      </c>
+      <c r="J6">
+        <v>0.12</v>
+      </c>
+      <c r="K6">
+        <v>2</v>
+      </c>
+      <c r="L6">
+        <v>0.5</v>
+      </c>
+      <c r="M6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7">
+        <v>40</v>
+      </c>
+      <c r="E7">
+        <v>5</v>
+      </c>
+      <c r="F7">
+        <v>5</v>
+      </c>
+      <c r="G7">
+        <v>7</v>
+      </c>
+      <c r="H7">
+        <v>6</v>
+      </c>
+      <c r="I7">
+        <v>0.1</v>
+      </c>
+      <c r="J7">
+        <v>0.12</v>
+      </c>
+      <c r="K7">
+        <v>2</v>
+      </c>
+      <c r="L7">
+        <v>0.5</v>
+      </c>
+      <c r="M7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8">
+        <v>40</v>
+      </c>
+      <c r="E8">
+        <v>5</v>
+      </c>
+      <c r="F8">
+        <v>5</v>
+      </c>
+      <c r="G8">
+        <v>7</v>
+      </c>
+      <c r="H8">
+        <v>6</v>
+      </c>
+      <c r="I8">
+        <v>0.1</v>
+      </c>
+      <c r="J8">
+        <v>0.12</v>
+      </c>
+      <c r="K8">
+        <v>2</v>
+      </c>
+      <c r="L8">
+        <v>0.5</v>
+      </c>
+      <c r="M8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9">
+        <v>40</v>
+      </c>
+      <c r="E9">
+        <v>5</v>
+      </c>
+      <c r="F9">
+        <v>5</v>
+      </c>
+      <c r="G9">
+        <v>7</v>
+      </c>
+      <c r="H9">
+        <v>6</v>
+      </c>
+      <c r="I9">
+        <v>0.1</v>
+      </c>
+      <c r="J9">
+        <v>0.12</v>
+      </c>
+      <c r="K9">
+        <v>2</v>
+      </c>
+      <c r="L9">
+        <v>0.5</v>
+      </c>
+      <c r="M9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10">
+        <v>40</v>
+      </c>
+      <c r="E10">
+        <v>5</v>
+      </c>
+      <c r="F10">
+        <v>5</v>
+      </c>
+      <c r="G10">
+        <v>7</v>
+      </c>
+      <c r="H10">
+        <v>6</v>
+      </c>
+      <c r="I10">
+        <v>0.1</v>
+      </c>
+      <c r="J10">
+        <v>0.12</v>
+      </c>
+      <c r="K10">
+        <v>2</v>
+      </c>
+      <c r="L10">
+        <v>0.5</v>
+      </c>
+      <c r="M10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11">
+        <v>40</v>
+      </c>
+      <c r="E11">
+        <v>5</v>
+      </c>
+      <c r="F11">
+        <v>5</v>
+      </c>
+      <c r="G11">
+        <v>7</v>
+      </c>
+      <c r="H11">
+        <v>6</v>
+      </c>
+      <c r="I11">
+        <v>0.1</v>
+      </c>
+      <c r="J11">
+        <v>0.12</v>
+      </c>
+      <c r="K11">
+        <v>2</v>
+      </c>
+      <c r="L11">
+        <v>0.5</v>
+      </c>
+      <c r="M11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12">
+        <v>40</v>
+      </c>
+      <c r="E12">
+        <v>5</v>
+      </c>
+      <c r="F12">
+        <v>5</v>
+      </c>
+      <c r="G12">
+        <v>7</v>
+      </c>
+      <c r="H12">
+        <v>6</v>
+      </c>
+      <c r="I12">
+        <v>0.1</v>
+      </c>
+      <c r="J12">
+        <v>0.12</v>
+      </c>
+      <c r="K12">
+        <v>2</v>
+      </c>
+      <c r="L12">
+        <v>0.5</v>
+      </c>
+      <c r="M12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13">
+        <v>40</v>
+      </c>
+      <c r="E13">
+        <v>5</v>
+      </c>
+      <c r="F13">
+        <v>5</v>
+      </c>
+      <c r="G13">
+        <v>7</v>
+      </c>
+      <c r="H13">
+        <v>6</v>
+      </c>
+      <c r="I13">
+        <v>0.1</v>
+      </c>
+      <c r="J13">
+        <v>0.12</v>
+      </c>
+      <c r="K13">
+        <v>2</v>
+      </c>
+      <c r="L13">
+        <v>0.5</v>
+      </c>
+      <c r="M13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14">
+        <v>40</v>
+      </c>
+      <c r="E14">
+        <v>5</v>
+      </c>
+      <c r="F14">
+        <v>5</v>
+      </c>
+      <c r="G14">
+        <v>7</v>
+      </c>
+      <c r="H14">
+        <v>6</v>
+      </c>
+      <c r="I14">
+        <v>0.1</v>
+      </c>
+      <c r="J14">
+        <v>0.12</v>
+      </c>
+      <c r="K14">
+        <v>2</v>
+      </c>
+      <c r="L14">
+        <v>0.5</v>
+      </c>
+      <c r="M14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15">
+        <v>40</v>
+      </c>
+      <c r="E15">
+        <v>5</v>
+      </c>
+      <c r="F15">
+        <v>5</v>
+      </c>
+      <c r="G15">
+        <v>7</v>
+      </c>
+      <c r="H15">
+        <v>6</v>
+      </c>
+      <c r="I15">
+        <v>0.1</v>
+      </c>
+      <c r="J15">
+        <v>0.12</v>
+      </c>
+      <c r="K15">
+        <v>2</v>
+      </c>
+      <c r="L15">
+        <v>0.5</v>
+      </c>
+      <c r="M15" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16">
+        <v>40</v>
+      </c>
+      <c r="E16">
+        <v>5</v>
+      </c>
+      <c r="F16">
+        <v>5</v>
+      </c>
+      <c r="G16">
+        <v>7</v>
+      </c>
+      <c r="H16">
+        <v>6</v>
+      </c>
+      <c r="I16">
+        <v>0.1</v>
+      </c>
+      <c r="J16">
+        <v>0.12</v>
+      </c>
+      <c r="K16">
+        <v>2</v>
+      </c>
+      <c r="L16">
+        <v>0.5</v>
+      </c>
+      <c r="M16" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17">
+        <v>40</v>
+      </c>
+      <c r="E17">
+        <v>5</v>
+      </c>
+      <c r="F17">
+        <v>5</v>
+      </c>
+      <c r="G17">
+        <v>7</v>
+      </c>
+      <c r="H17">
+        <v>6</v>
+      </c>
+      <c r="I17">
+        <v>0.1</v>
+      </c>
+      <c r="J17">
+        <v>0.12</v>
+      </c>
+      <c r="K17">
+        <v>2</v>
+      </c>
+      <c r="L17">
+        <v>0.5</v>
+      </c>
+      <c r="M17" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E49C5A42-5AA9-4484-8593-A550BEA149B1}">
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="2" max="2" width="13.68359375" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="12.7890625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.26171875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="b">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>20</v>
+      </c>
+      <c r="E2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>50</v>
+      </c>
+      <c r="E3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="b">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>20</v>
+      </c>
+      <c r="E4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="b">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>20</v>
+      </c>
+      <c r="E5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="b">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>20</v>
+      </c>
+      <c r="E6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>20</v>
+      </c>
+      <c r="E7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" t="b">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>20</v>
+      </c>
+      <c r="E8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>20</v>
+      </c>
+      <c r="E9">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" t="b">
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>20</v>
+      </c>
+      <c r="E10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11" t="b">
+        <v>0</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>20</v>
+      </c>
+      <c r="E11">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12" t="b">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>20</v>
+      </c>
+      <c r="E12">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13" t="b">
+        <v>1</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>20</v>
+      </c>
+      <c r="E13">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14" t="b">
+        <v>1</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>20</v>
+      </c>
+      <c r="E14">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15" t="b">
+        <v>1</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>20</v>
+      </c>
+      <c r="E15">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16" t="b">
+        <v>0</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>20</v>
+      </c>
+      <c r="E16">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17" t="b">
+        <v>0</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>20</v>
+      </c>
+      <c r="E17">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACB49812-9D86-4204-944A-0BDF9B6E9617}">
+  <dimension ref="A1:B17"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="2" max="2" width="12.89453125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/experiment/template/experiment_configurations.xlsx
+++ b/experiment/template/experiment_configurations.xlsx
@@ -1,24 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nb\Dropbox\PC\Desktop\share\git\photo-stepped-dpu\photo-dpu\experiment\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{557FD0ED-339C-4595-8746-0D9257630E9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A9A8CEA-10E5-49B0-940B-CD2CD2185074}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13992" tabRatio="696" xr2:uid="{AF0A681E-4FC9-47B3-B0CB-C8A6E2C1048C}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13992" tabRatio="696" activeTab="1" xr2:uid="{AF0A681E-4FC9-47B3-B0CB-C8A6E2C1048C}"/>
   </bookViews>
   <sheets>
-    <sheet name="light-control" sheetId="6" r:id="rId1"/>
-    <sheet name="light-step_generation" sheetId="7" r:id="rId2"/>
-    <sheet name="light-steps" sheetId="8" r:id="rId3"/>
-    <sheet name="selection-control" sheetId="3" r:id="rId4"/>
-    <sheet name="selection-step_generation" sheetId="5" r:id="rId5"/>
-    <sheet name="selection-steps" sheetId="2" r:id="rId6"/>
+    <sheet name="light2-control" sheetId="6" r:id="rId1"/>
+    <sheet name="light2-step_generation" sheetId="7" r:id="rId2"/>
+    <sheet name="light2-steps" sheetId="8" r:id="rId3"/>
+    <sheet name="light3-control" sheetId="9" r:id="rId4"/>
+    <sheet name="light3-step_generation" sheetId="10" r:id="rId5"/>
+    <sheet name="light3-steps" sheetId="11" r:id="rId6"/>
+    <sheet name="selection-control" sheetId="3" r:id="rId7"/>
+    <sheet name="selection-step_generation" sheetId="5" r:id="rId8"/>
+    <sheet name="selection-steps" sheetId="2" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -260,6 +263,220 @@
     <author>nb</author>
   </authors>
   <commentList>
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{E0136C7B-4EEE-4A58-BDFB-F98EBCE27C5C}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Case insensitive. AUTO if you want to automatically calculate steps; MANUAL if you want to manually input each step; OFF to not do selection</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{25DB91A7-92FE-44F0-BC5A-04EEB347DE1C}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>chemical: using a chemical selection. Slow pumps will be used to adjust chemical concentration
+non-chemical: anything that does not require fluidics</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{32E7E1DC-685E-4978-BC62-E52592FE5BCA}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>number of growth curves required at start of experiment before beginning selection</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{15FF9316-5E9D-430D-8984-AB0D8F80A27D}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>number of growth curves to wait before increasing selection</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{240AA7CF-7BEB-49CA-9415-6CAC33F30949}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>hours; minimum time to spend on a step before increasing or decreasing selection; a reasonable value is at least one full doubling</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{580FB46D-3CA4-4EEA-9271-0E3AC68CC997}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>hours; if growth rate measurement is stalled for this many hours, selection pressure will be eased</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{07349474-94AD-418B-BF59-710D80B9B290}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>growth rate which triggers increase in selection; for example, if growth rate is 0.1, consider making the max_growthrate 0.06</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0" shapeId="0" xr:uid="{1B69EF04-87FC-4894-B7B0-55CC278DD945}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>lowest growth rate allowable for selection; if growth rate is less than this, selection pressure will be eased</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M1" authorId="0" shapeId="0" xr:uid="{CC5CBCDE-FAA5-4E1D-9980-4A24372B58B2}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>mostly for logging purposes</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>nb</author>
+  </authors>
+  <commentList>
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{D86DC7EE-D1C9-43D2-8C34-3A7DD1A48531}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>True if you want logarithmic steps; False if linear</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{06518C56-ED99-4566-A80A-F82C4D195A43}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>first step value. Goes to 0 if we are decreasing selection further</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{0259502B-649B-433E-8F1E-6D87894AA4A3}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>maximum value your selection can go to; for chemical selection = proportion of stock concentration (don't want to use all of stock)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{A449D673-5192-442F-BB4A-C9472F2790DA}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>number of steps between min_selection and max_selection</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>nb</author>
+  </authors>
+  <commentList>
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{F5126A85-6A13-43CC-99FA-1B03AF3D0C1A}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>for manual setting of steps. Should be a comma separated list ie 
+0.1,0.2,0.5,0.75,1</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>nb</author>
+  </authors>
+  <commentList>
     <comment ref="B1" authorId="0" shapeId="0" xr:uid="{C06F9245-8FF8-49AE-B4C8-449719000C1A}">
       <text>
         <r>
@@ -422,7 +639,7 @@
 </comments>
 </file>
 
-<file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments8.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>nb</author>
@@ -484,7 +701,7 @@
 </comments>
 </file>
 
-<file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments9.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>nb</author>
@@ -509,7 +726,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="30">
   <si>
     <t>vial</t>
   </si>
@@ -1066,7 +1283,7 @@
         <v>5</v>
       </c>
       <c r="C2">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D2">
         <v>250</v>
@@ -1107,7 +1324,7 @@
         <v>5</v>
       </c>
       <c r="C3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D3">
         <v>250</v>
@@ -1148,7 +1365,7 @@
         <v>5</v>
       </c>
       <c r="C4">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D4">
         <v>250</v>
@@ -1189,7 +1406,7 @@
         <v>5</v>
       </c>
       <c r="C5">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D5">
         <v>250</v>
@@ -1230,7 +1447,7 @@
         <v>5</v>
       </c>
       <c r="C6">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D6">
         <v>250</v>
@@ -1271,7 +1488,7 @@
         <v>5</v>
       </c>
       <c r="C7">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D7">
         <v>250</v>
@@ -1312,7 +1529,7 @@
         <v>5</v>
       </c>
       <c r="C8">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D8">
         <v>250</v>
@@ -1353,7 +1570,7 @@
         <v>5</v>
       </c>
       <c r="C9">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D9">
         <v>250</v>
@@ -1394,7 +1611,7 @@
         <v>5</v>
       </c>
       <c r="C10">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D10">
         <v>250</v>
@@ -1435,7 +1652,7 @@
         <v>5</v>
       </c>
       <c r="C11">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D11">
         <v>250</v>
@@ -1476,7 +1693,7 @@
         <v>5</v>
       </c>
       <c r="C12">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D12">
         <v>250</v>
@@ -1517,7 +1734,7 @@
         <v>5</v>
       </c>
       <c r="C13">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D13">
         <v>250</v>
@@ -1558,7 +1775,7 @@
         <v>5</v>
       </c>
       <c r="C14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D14">
         <v>250</v>
@@ -1599,7 +1816,7 @@
         <v>5</v>
       </c>
       <c r="C15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D15">
         <v>250</v>
@@ -1640,7 +1857,7 @@
         <v>5</v>
       </c>
       <c r="C16">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D16">
         <v>250</v>
@@ -1681,7 +1898,7 @@
         <v>5</v>
       </c>
       <c r="C17">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D17">
         <v>250</v>
@@ -1766,10 +1983,10 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="D2">
-        <v>3000</v>
+        <v>1500</v>
       </c>
       <c r="E2">
         <v>20</v>
@@ -1783,10 +2000,10 @@
         <v>1</v>
       </c>
       <c r="C3">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="D3">
-        <v>3000</v>
+        <v>1500</v>
       </c>
       <c r="E3">
         <v>20</v>
@@ -1800,10 +2017,10 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="D4">
-        <v>3000</v>
+        <v>1500</v>
       </c>
       <c r="E4">
         <v>20</v>
@@ -1817,10 +2034,10 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="D5">
-        <v>3000</v>
+        <v>1500</v>
       </c>
       <c r="E5">
         <v>20</v>
@@ -1834,10 +2051,10 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="D6">
-        <v>3000</v>
+        <v>1500</v>
       </c>
       <c r="E6">
         <v>20</v>
@@ -1851,10 +2068,10 @@
         <v>0</v>
       </c>
       <c r="C7">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="D7">
-        <v>3000</v>
+        <v>1500</v>
       </c>
       <c r="E7">
         <v>20</v>
@@ -1868,10 +2085,10 @@
         <v>0</v>
       </c>
       <c r="C8">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="D8">
-        <v>3000</v>
+        <v>1500</v>
       </c>
       <c r="E8">
         <v>20</v>
@@ -1885,10 +2102,10 @@
         <v>0</v>
       </c>
       <c r="C9">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="D9">
-        <v>3000</v>
+        <v>1500</v>
       </c>
       <c r="E9">
         <v>20</v>
@@ -1902,10 +2119,10 @@
         <v>0</v>
       </c>
       <c r="C10">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="D10">
-        <v>3000</v>
+        <v>1500</v>
       </c>
       <c r="E10">
         <v>20</v>
@@ -1919,10 +2136,10 @@
         <v>0</v>
       </c>
       <c r="C11">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="D11">
-        <v>3000</v>
+        <v>1500</v>
       </c>
       <c r="E11">
         <v>20</v>
@@ -1936,10 +2153,10 @@
         <v>1</v>
       </c>
       <c r="C12">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="D12">
-        <v>3000</v>
+        <v>1500</v>
       </c>
       <c r="E12">
         <v>20</v>
@@ -1953,10 +2170,10 @@
         <v>1</v>
       </c>
       <c r="C13">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="D13">
-        <v>3000</v>
+        <v>1500</v>
       </c>
       <c r="E13">
         <v>20</v>
@@ -1970,10 +2187,10 @@
         <v>1</v>
       </c>
       <c r="C14">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="D14">
-        <v>3000</v>
+        <v>1500</v>
       </c>
       <c r="E14">
         <v>20</v>
@@ -1987,10 +2204,10 @@
         <v>1</v>
       </c>
       <c r="C15">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="D15">
-        <v>3000</v>
+        <v>1500</v>
       </c>
       <c r="E15">
         <v>20</v>
@@ -2004,10 +2221,10 @@
         <v>0</v>
       </c>
       <c r="C16">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="D16">
-        <v>3000</v>
+        <v>1500</v>
       </c>
       <c r="E16">
         <v>20</v>
@@ -2021,10 +2238,10 @@
         <v>0</v>
       </c>
       <c r="C17">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="D17">
-        <v>3000</v>
+        <v>1500</v>
       </c>
       <c r="E17">
         <v>20</v>
@@ -2187,6 +2404,1195 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CA9B935-740F-4BAF-8AEF-C11C83975B93}">
+  <dimension ref="A1:M17"/>
+  <sheetFormatPr defaultColWidth="8.83984375" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="5.83984375" customWidth="1"/>
+    <col min="2" max="2" width="14.20703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.1015625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.20703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.15625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.9453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.47265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.15625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.05078125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.3671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.83984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.15625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.62890625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="3">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <v>100</v>
+      </c>
+      <c r="D2">
+        <v>250</v>
+      </c>
+      <c r="E2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2">
+        <v>5</v>
+      </c>
+      <c r="H2">
+        <v>5</v>
+      </c>
+      <c r="I2">
+        <v>7</v>
+      </c>
+      <c r="J2">
+        <v>6</v>
+      </c>
+      <c r="K2">
+        <v>0.08</v>
+      </c>
+      <c r="L2">
+        <v>0.1</v>
+      </c>
+      <c r="M2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>5</v>
+      </c>
+      <c r="C3">
+        <v>100</v>
+      </c>
+      <c r="D3">
+        <v>250</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G3">
+        <v>5</v>
+      </c>
+      <c r="H3">
+        <v>5</v>
+      </c>
+      <c r="I3">
+        <v>7</v>
+      </c>
+      <c r="J3">
+        <v>6</v>
+      </c>
+      <c r="K3">
+        <v>0.08</v>
+      </c>
+      <c r="L3">
+        <v>0.1</v>
+      </c>
+      <c r="M3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="3">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>100</v>
+      </c>
+      <c r="D4">
+        <v>250</v>
+      </c>
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4">
+        <v>5</v>
+      </c>
+      <c r="H4">
+        <v>5</v>
+      </c>
+      <c r="I4">
+        <v>7</v>
+      </c>
+      <c r="J4">
+        <v>6</v>
+      </c>
+      <c r="K4">
+        <v>0.08</v>
+      </c>
+      <c r="L4">
+        <v>0.1</v>
+      </c>
+      <c r="M4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="3">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>100</v>
+      </c>
+      <c r="D5">
+        <v>250</v>
+      </c>
+      <c r="E5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5">
+        <v>5</v>
+      </c>
+      <c r="H5">
+        <v>5</v>
+      </c>
+      <c r="I5">
+        <v>7</v>
+      </c>
+      <c r="J5">
+        <v>6</v>
+      </c>
+      <c r="K5">
+        <v>0.08</v>
+      </c>
+      <c r="L5">
+        <v>0.1</v>
+      </c>
+      <c r="M5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="3">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>100</v>
+      </c>
+      <c r="D6">
+        <v>250</v>
+      </c>
+      <c r="E6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+      <c r="H6">
+        <v>5</v>
+      </c>
+      <c r="I6">
+        <v>7</v>
+      </c>
+      <c r="J6">
+        <v>6</v>
+      </c>
+      <c r="K6">
+        <v>0.08</v>
+      </c>
+      <c r="L6">
+        <v>0.1</v>
+      </c>
+      <c r="M6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="3">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7">
+        <v>100</v>
+      </c>
+      <c r="D7">
+        <v>250</v>
+      </c>
+      <c r="E7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" t="s">
+        <v>28</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+      <c r="H7">
+        <v>5</v>
+      </c>
+      <c r="I7">
+        <v>7</v>
+      </c>
+      <c r="J7">
+        <v>6</v>
+      </c>
+      <c r="K7">
+        <v>0.08</v>
+      </c>
+      <c r="L7">
+        <v>0.1</v>
+      </c>
+      <c r="M7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="3">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>5</v>
+      </c>
+      <c r="C8">
+        <v>100</v>
+      </c>
+      <c r="D8">
+        <v>250</v>
+      </c>
+      <c r="E8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G8">
+        <v>5</v>
+      </c>
+      <c r="H8">
+        <v>5</v>
+      </c>
+      <c r="I8">
+        <v>7</v>
+      </c>
+      <c r="J8">
+        <v>6</v>
+      </c>
+      <c r="K8">
+        <v>0.08</v>
+      </c>
+      <c r="L8">
+        <v>0.1</v>
+      </c>
+      <c r="M8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="3">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>5</v>
+      </c>
+      <c r="C9">
+        <v>100</v>
+      </c>
+      <c r="D9">
+        <v>250</v>
+      </c>
+      <c r="E9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" t="s">
+        <v>28</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+      <c r="H9">
+        <v>5</v>
+      </c>
+      <c r="I9">
+        <v>7</v>
+      </c>
+      <c r="J9">
+        <v>6</v>
+      </c>
+      <c r="K9">
+        <v>0.08</v>
+      </c>
+      <c r="L9">
+        <v>0.1</v>
+      </c>
+      <c r="M9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="3">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>5</v>
+      </c>
+      <c r="C10">
+        <v>100</v>
+      </c>
+      <c r="D10">
+        <v>250</v>
+      </c>
+      <c r="E10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" t="s">
+        <v>28</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+      <c r="H10">
+        <v>5</v>
+      </c>
+      <c r="I10">
+        <v>7</v>
+      </c>
+      <c r="J10">
+        <v>6</v>
+      </c>
+      <c r="K10">
+        <v>0.08</v>
+      </c>
+      <c r="L10">
+        <v>0.1</v>
+      </c>
+      <c r="M10" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="3">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>5</v>
+      </c>
+      <c r="C11">
+        <v>100</v>
+      </c>
+      <c r="D11">
+        <v>250</v>
+      </c>
+      <c r="E11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" t="s">
+        <v>28</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+      <c r="H11">
+        <v>5</v>
+      </c>
+      <c r="I11">
+        <v>7</v>
+      </c>
+      <c r="J11">
+        <v>6</v>
+      </c>
+      <c r="K11">
+        <v>0.08</v>
+      </c>
+      <c r="L11">
+        <v>0.1</v>
+      </c>
+      <c r="M11" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="3">
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <v>5</v>
+      </c>
+      <c r="C12">
+        <v>100</v>
+      </c>
+      <c r="D12">
+        <v>250</v>
+      </c>
+      <c r="E12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" t="s">
+        <v>28</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+      <c r="H12">
+        <v>5</v>
+      </c>
+      <c r="I12">
+        <v>7</v>
+      </c>
+      <c r="J12">
+        <v>6</v>
+      </c>
+      <c r="K12">
+        <v>0.08</v>
+      </c>
+      <c r="L12">
+        <v>0.1</v>
+      </c>
+      <c r="M12" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="3">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <v>5</v>
+      </c>
+      <c r="C13">
+        <v>100</v>
+      </c>
+      <c r="D13">
+        <v>250</v>
+      </c>
+      <c r="E13" t="s">
+        <v>19</v>
+      </c>
+      <c r="F13" t="s">
+        <v>28</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+      <c r="H13">
+        <v>5</v>
+      </c>
+      <c r="I13">
+        <v>7</v>
+      </c>
+      <c r="J13">
+        <v>6</v>
+      </c>
+      <c r="K13">
+        <v>0.08</v>
+      </c>
+      <c r="L13">
+        <v>0.1</v>
+      </c>
+      <c r="M13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="3">
+        <v>12</v>
+      </c>
+      <c r="B14">
+        <v>5</v>
+      </c>
+      <c r="C14">
+        <v>100</v>
+      </c>
+      <c r="D14">
+        <v>250</v>
+      </c>
+      <c r="E14" t="s">
+        <v>19</v>
+      </c>
+      <c r="F14" t="s">
+        <v>28</v>
+      </c>
+      <c r="G14">
+        <v>5</v>
+      </c>
+      <c r="H14">
+        <v>5</v>
+      </c>
+      <c r="I14">
+        <v>7</v>
+      </c>
+      <c r="J14">
+        <v>6</v>
+      </c>
+      <c r="K14">
+        <v>0.08</v>
+      </c>
+      <c r="L14">
+        <v>0.1</v>
+      </c>
+      <c r="M14" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="3">
+        <v>13</v>
+      </c>
+      <c r="B15">
+        <v>5</v>
+      </c>
+      <c r="C15">
+        <v>100</v>
+      </c>
+      <c r="D15">
+        <v>250</v>
+      </c>
+      <c r="E15" t="s">
+        <v>19</v>
+      </c>
+      <c r="F15" t="s">
+        <v>28</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+      <c r="H15">
+        <v>5</v>
+      </c>
+      <c r="I15">
+        <v>7</v>
+      </c>
+      <c r="J15">
+        <v>6</v>
+      </c>
+      <c r="K15">
+        <v>0.08</v>
+      </c>
+      <c r="L15">
+        <v>0.1</v>
+      </c>
+      <c r="M15" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="3">
+        <v>14</v>
+      </c>
+      <c r="B16">
+        <v>5</v>
+      </c>
+      <c r="C16">
+        <v>100</v>
+      </c>
+      <c r="D16">
+        <v>250</v>
+      </c>
+      <c r="E16" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" t="s">
+        <v>28</v>
+      </c>
+      <c r="G16">
+        <v>5</v>
+      </c>
+      <c r="H16">
+        <v>5</v>
+      </c>
+      <c r="I16">
+        <v>7</v>
+      </c>
+      <c r="J16">
+        <v>6</v>
+      </c>
+      <c r="K16">
+        <v>0.08</v>
+      </c>
+      <c r="L16">
+        <v>0.1</v>
+      </c>
+      <c r="M16" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="3">
+        <v>15</v>
+      </c>
+      <c r="B17">
+        <v>5</v>
+      </c>
+      <c r="C17">
+        <v>100</v>
+      </c>
+      <c r="D17">
+        <v>250</v>
+      </c>
+      <c r="E17" t="s">
+        <v>19</v>
+      </c>
+      <c r="F17" t="s">
+        <v>28</v>
+      </c>
+      <c r="G17">
+        <v>5</v>
+      </c>
+      <c r="H17">
+        <v>5</v>
+      </c>
+      <c r="I17">
+        <v>7</v>
+      </c>
+      <c r="J17">
+        <v>6</v>
+      </c>
+      <c r="K17">
+        <v>0.08</v>
+      </c>
+      <c r="L17">
+        <v>0.1</v>
+      </c>
+      <c r="M17" t="s">
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F2:F17">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A9B4294-3FA5-45A6-B166-A8D0423D3D74}">
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="2" max="2" width="13.68359375" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="12.7890625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.26171875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="b">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>1000</v>
+      </c>
+      <c r="D2">
+        <v>3000</v>
+      </c>
+      <c r="E2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>1000</v>
+      </c>
+      <c r="D3">
+        <v>3000</v>
+      </c>
+      <c r="E3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="b">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>1000</v>
+      </c>
+      <c r="D4">
+        <v>3000</v>
+      </c>
+      <c r="E4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="b">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>1000</v>
+      </c>
+      <c r="D5">
+        <v>3000</v>
+      </c>
+      <c r="E5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="b">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>1000</v>
+      </c>
+      <c r="D6">
+        <v>3000</v>
+      </c>
+      <c r="E6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>1000</v>
+      </c>
+      <c r="D7">
+        <v>3000</v>
+      </c>
+      <c r="E7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" t="b">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>1000</v>
+      </c>
+      <c r="D8">
+        <v>3000</v>
+      </c>
+      <c r="E8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <v>1000</v>
+      </c>
+      <c r="D9">
+        <v>3000</v>
+      </c>
+      <c r="E9">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" t="b">
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <v>1000</v>
+      </c>
+      <c r="D10">
+        <v>3000</v>
+      </c>
+      <c r="E10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11" t="b">
+        <v>0</v>
+      </c>
+      <c r="C11">
+        <v>1000</v>
+      </c>
+      <c r="D11">
+        <v>3000</v>
+      </c>
+      <c r="E11">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12" t="b">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>1000</v>
+      </c>
+      <c r="D12">
+        <v>3000</v>
+      </c>
+      <c r="E12">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13" t="b">
+        <v>1</v>
+      </c>
+      <c r="C13">
+        <v>1000</v>
+      </c>
+      <c r="D13">
+        <v>3000</v>
+      </c>
+      <c r="E13">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14" t="b">
+        <v>1</v>
+      </c>
+      <c r="C14">
+        <v>1000</v>
+      </c>
+      <c r="D14">
+        <v>3000</v>
+      </c>
+      <c r="E14">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15" t="b">
+        <v>1</v>
+      </c>
+      <c r="C15">
+        <v>1000</v>
+      </c>
+      <c r="D15">
+        <v>3000</v>
+      </c>
+      <c r="E15">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16" t="b">
+        <v>0</v>
+      </c>
+      <c r="C16">
+        <v>1000</v>
+      </c>
+      <c r="D16">
+        <v>3000</v>
+      </c>
+      <c r="E16">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17" t="b">
+        <v>0</v>
+      </c>
+      <c r="C17">
+        <v>1000</v>
+      </c>
+      <c r="D17">
+        <v>3000</v>
+      </c>
+      <c r="E17">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6270CC91-C7EB-4578-B7FC-A30C86D3E7B4}">
+  <dimension ref="A1:B17"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="2" max="2" width="12.89453125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A245ECA0-28EC-4A16-B4DE-14A4BDF7F5DD}">
   <dimension ref="A1:M17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
@@ -2908,7 +4314,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E49C5A42-5AA9-4484-8593-A550BEA149B1}">
   <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
@@ -3213,7 +4619,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACB49812-9D86-4204-944A-0BDF9B6E9617}">
   <dimension ref="A1:B17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>

--- a/experiment/template/experiment_configurations.xlsx
+++ b/experiment/template/experiment_configurations.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nb\Dropbox\PC\Desktop\share\git\photo-stepped-dpu\photo-dpu\experiment\template\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nb\Dropbox\eVOLVER\dpu\experiment\250522_Bcarotene_campaignB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A9A8CEA-10E5-49B0-940B-CD2CD2185074}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F2C0B1B-103F-4007-943C-204218A68C19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13992" tabRatio="696" activeTab="1" xr2:uid="{AF0A681E-4FC9-47B3-B0CB-C8A6E2C1048C}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13992" tabRatio="696" xr2:uid="{AF0A681E-4FC9-47B3-B0CB-C8A6E2C1048C}"/>
   </bookViews>
   <sheets>
     <sheet name="light2-control" sheetId="6" r:id="rId1"/>
@@ -49,6 +49,19 @@
     <author>nb</author>
   </authors>
   <commentList>
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{C7939B78-E7C1-44E0-8BD7-8CF6B8FE3D3F}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>The light setting after acclimation_light. Used only when step_type is OFF</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="E1" authorId="0" shapeId="0" xr:uid="{2BCF1934-CA14-4558-8F85-4CB590F9F593}">
       <text>
         <r>
@@ -69,7 +82,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>chemical: using a chemical selection. Slow pumps will be used to adjust chemical concentration
 non-chemical: anything that does not require fluidics</t>
@@ -115,7 +128,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{1D231594-1049-4CF2-B10D-FD3A2CC477F2}">
+    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{BABEFDAC-9693-4316-93B2-0A879CF5E39D}">
       <text>
         <r>
           <rPr>
@@ -263,6 +276,19 @@
     <author>nb</author>
   </authors>
   <commentList>
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{F4675255-C750-4031-960E-F917374B9C32}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>The light setting after acclimation_light. Used only when step_type is OFF</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="E1" authorId="0" shapeId="0" xr:uid="{E0136C7B-4EEE-4A58-BDFB-F98EBCE27C5C}">
       <text>
         <r>
@@ -283,7 +309,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>chemical: using a chemical selection. Slow pumps will be used to adjust chemical concentration
 non-chemical: anything that does not require fluidics</t>
@@ -321,7 +347,7 @@
         <r>
           <rPr>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -329,7 +355,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{580FB46D-3CA4-4EEA-9271-0E3AC68CC997}">
+    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{91DA765D-D785-470D-93F6-2FAAF8444E9D}">
       <text>
         <r>
           <rPr>
@@ -497,7 +523,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>chemical: using a chemical selection. Slow pumps will be used to adjust chemical concentration
 non-chemical: anything that does not require fluidics</t>
@@ -556,7 +582,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{E36F93DF-EBE8-44D1-AF93-062AA8622028}">
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{C999DEDB-EEA4-470C-BE37-69A8EBF7FF75}">
       <text>
         <r>
           <rPr>
@@ -726,7 +752,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="29">
   <si>
     <t>vial</t>
   </si>
@@ -785,12 +811,6 @@
     <t>stock_concentration</t>
   </si>
   <si>
-    <t>AUTO</t>
-  </si>
-  <si>
-    <t>MANUAL</t>
-  </si>
-  <si>
     <t>OFF</t>
   </si>
   <si>
@@ -815,7 +835,10 @@
     <t>non-chemical</t>
   </si>
   <si>
-    <t>µE per m^2 per s</t>
+    <t>AUTO</t>
+  </si>
+  <si>
+    <t>uE per m^2 per s</t>
   </si>
 </sst>
 </file>
@@ -846,9 +869,9 @@
     </font>
     <font>
       <sz val="9"/>
-      <color indexed="81"/>
+      <color rgb="FF000000"/>
       <name val="Tahoma"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1220,18 +1243,16 @@
   <sheetFormatPr defaultColWidth="8.83984375" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="5.83984375" customWidth="1"/>
-    <col min="2" max="2" width="14.20703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.1015625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.20703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.15625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.9453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="14.15625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="8.15625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.47265625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="17.15625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.05078125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.3671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.3125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12.83984375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="13.15625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.62890625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.68359375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -1239,19 +1260,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>27</v>
-      </c>
       <c r="E1" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>2</v>
@@ -1280,40 +1301,40 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="E2" t="s">
         <v>19</v>
       </c>
       <c r="F2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2">
+        <v>5</v>
+      </c>
+      <c r="H2">
+        <v>5</v>
+      </c>
+      <c r="I2">
+        <v>12</v>
+      </c>
+      <c r="J2">
+        <v>6</v>
+      </c>
+      <c r="K2">
+        <v>0.1</v>
+      </c>
+      <c r="L2">
+        <v>0.12</v>
+      </c>
+      <c r="M2" t="s">
         <v>28</v>
-      </c>
-      <c r="G2">
-        <v>5</v>
-      </c>
-      <c r="H2">
-        <v>5</v>
-      </c>
-      <c r="I2">
-        <v>7</v>
-      </c>
-      <c r="J2">
-        <v>6</v>
-      </c>
-      <c r="K2">
-        <v>0.08</v>
-      </c>
-      <c r="L2">
-        <v>0.1</v>
-      </c>
-      <c r="M2" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -1321,40 +1342,40 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="E3" t="s">
         <v>19</v>
       </c>
       <c r="F3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3">
+        <v>5</v>
+      </c>
+      <c r="H3">
+        <v>5</v>
+      </c>
+      <c r="I3">
+        <v>12</v>
+      </c>
+      <c r="J3">
+        <v>6</v>
+      </c>
+      <c r="K3">
+        <v>0.1</v>
+      </c>
+      <c r="L3">
+        <v>0.12</v>
+      </c>
+      <c r="M3" t="s">
         <v>28</v>
-      </c>
-      <c r="G3">
-        <v>5</v>
-      </c>
-      <c r="H3">
-        <v>5</v>
-      </c>
-      <c r="I3">
-        <v>7</v>
-      </c>
-      <c r="J3">
-        <v>6</v>
-      </c>
-      <c r="K3">
-        <v>0.08</v>
-      </c>
-      <c r="L3">
-        <v>0.1</v>
-      </c>
-      <c r="M3" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -1362,40 +1383,40 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="C4">
         <v>0</v>
       </c>
       <c r="D4">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="E4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="F4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4">
+        <v>5</v>
+      </c>
+      <c r="H4">
+        <v>5</v>
+      </c>
+      <c r="I4">
+        <v>12</v>
+      </c>
+      <c r="J4">
+        <v>6</v>
+      </c>
+      <c r="K4">
+        <v>0.1</v>
+      </c>
+      <c r="L4">
+        <v>0.12</v>
+      </c>
+      <c r="M4" t="s">
         <v>28</v>
-      </c>
-      <c r="G4">
-        <v>5</v>
-      </c>
-      <c r="H4">
-        <v>5</v>
-      </c>
-      <c r="I4">
-        <v>7</v>
-      </c>
-      <c r="J4">
-        <v>6</v>
-      </c>
-      <c r="K4">
-        <v>0.08</v>
-      </c>
-      <c r="L4">
-        <v>0.1</v>
-      </c>
-      <c r="M4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -1403,40 +1424,40 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="E5" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="F5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5">
+        <v>5</v>
+      </c>
+      <c r="H5">
+        <v>5</v>
+      </c>
+      <c r="I5">
+        <v>12</v>
+      </c>
+      <c r="J5">
+        <v>6</v>
+      </c>
+      <c r="K5">
+        <v>0.1</v>
+      </c>
+      <c r="L5">
+        <v>0.12</v>
+      </c>
+      <c r="M5" t="s">
         <v>28</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-      <c r="H5">
-        <v>5</v>
-      </c>
-      <c r="I5">
-        <v>7</v>
-      </c>
-      <c r="J5">
-        <v>6</v>
-      </c>
-      <c r="K5">
-        <v>0.08</v>
-      </c>
-      <c r="L5">
-        <v>0.1</v>
-      </c>
-      <c r="M5" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -1444,40 +1465,40 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="E6" t="s">
         <v>19</v>
       </c>
       <c r="F6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+      <c r="H6">
+        <v>5</v>
+      </c>
+      <c r="I6">
+        <v>12</v>
+      </c>
+      <c r="J6">
+        <v>6</v>
+      </c>
+      <c r="K6">
+        <v>0.02</v>
+      </c>
+      <c r="L6">
+        <v>0.06</v>
+      </c>
+      <c r="M6" t="s">
         <v>28</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-      <c r="H6">
-        <v>5</v>
-      </c>
-      <c r="I6">
-        <v>7</v>
-      </c>
-      <c r="J6">
-        <v>6</v>
-      </c>
-      <c r="K6">
-        <v>0.08</v>
-      </c>
-      <c r="L6">
-        <v>0.1</v>
-      </c>
-      <c r="M6" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -1485,40 +1506,40 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="C7">
         <v>0</v>
       </c>
       <c r="D7">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="E7" t="s">
         <v>19</v>
       </c>
       <c r="F7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+      <c r="H7">
+        <v>5</v>
+      </c>
+      <c r="I7">
+        <v>12</v>
+      </c>
+      <c r="J7">
+        <v>6</v>
+      </c>
+      <c r="K7">
+        <v>0.02</v>
+      </c>
+      <c r="L7">
+        <v>0.06</v>
+      </c>
+      <c r="M7" t="s">
         <v>28</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-      <c r="H7">
-        <v>5</v>
-      </c>
-      <c r="I7">
-        <v>7</v>
-      </c>
-      <c r="J7">
-        <v>6</v>
-      </c>
-      <c r="K7">
-        <v>0.08</v>
-      </c>
-      <c r="L7">
-        <v>0.1</v>
-      </c>
-      <c r="M7" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -1526,40 +1547,40 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="C8">
         <v>0</v>
       </c>
       <c r="D8">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="E8" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="F8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G8">
+        <v>5</v>
+      </c>
+      <c r="H8">
+        <v>5</v>
+      </c>
+      <c r="I8">
+        <v>12</v>
+      </c>
+      <c r="J8">
+        <v>6</v>
+      </c>
+      <c r="K8">
+        <v>0.02</v>
+      </c>
+      <c r="L8">
+        <v>0.06</v>
+      </c>
+      <c r="M8" t="s">
         <v>28</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-      <c r="H8">
-        <v>5</v>
-      </c>
-      <c r="I8">
-        <v>7</v>
-      </c>
-      <c r="J8">
-        <v>6</v>
-      </c>
-      <c r="K8">
-        <v>0.08</v>
-      </c>
-      <c r="L8">
-        <v>0.1</v>
-      </c>
-      <c r="M8" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -1567,40 +1588,40 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="F9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+      <c r="H9">
+        <v>5</v>
+      </c>
+      <c r="I9">
+        <v>12</v>
+      </c>
+      <c r="J9">
+        <v>6</v>
+      </c>
+      <c r="K9">
+        <v>0.02</v>
+      </c>
+      <c r="L9">
+        <v>0.06</v>
+      </c>
+      <c r="M9" t="s">
         <v>28</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-      <c r="H9">
-        <v>5</v>
-      </c>
-      <c r="I9">
-        <v>7</v>
-      </c>
-      <c r="J9">
-        <v>6</v>
-      </c>
-      <c r="K9">
-        <v>0.08</v>
-      </c>
-      <c r="L9">
-        <v>0.1</v>
-      </c>
-      <c r="M9" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -1608,40 +1629,40 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="E10" t="s">
         <v>19</v>
       </c>
       <c r="F10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+      <c r="H10">
+        <v>5</v>
+      </c>
+      <c r="I10">
+        <v>12</v>
+      </c>
+      <c r="J10">
+        <v>6</v>
+      </c>
+      <c r="K10">
+        <v>0.02</v>
+      </c>
+      <c r="L10">
+        <v>0.06</v>
+      </c>
+      <c r="M10" t="s">
         <v>28</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-      <c r="H10">
-        <v>5</v>
-      </c>
-      <c r="I10">
-        <v>7</v>
-      </c>
-      <c r="J10">
-        <v>6</v>
-      </c>
-      <c r="K10">
-        <v>0.08</v>
-      </c>
-      <c r="L10">
-        <v>0.1</v>
-      </c>
-      <c r="M10" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -1649,40 +1670,40 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="E11" t="s">
         <v>19</v>
       </c>
       <c r="F11" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+      <c r="H11">
+        <v>5</v>
+      </c>
+      <c r="I11">
+        <v>12</v>
+      </c>
+      <c r="J11">
+        <v>6</v>
+      </c>
+      <c r="K11">
+        <v>0.02</v>
+      </c>
+      <c r="L11">
+        <v>0.06</v>
+      </c>
+      <c r="M11" t="s">
         <v>28</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-      <c r="H11">
-        <v>5</v>
-      </c>
-      <c r="I11">
-        <v>7</v>
-      </c>
-      <c r="J11">
-        <v>6</v>
-      </c>
-      <c r="K11">
-        <v>0.08</v>
-      </c>
-      <c r="L11">
-        <v>0.1</v>
-      </c>
-      <c r="M11" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -1690,40 +1711,40 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="E12" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="F12" t="s">
+        <v>26</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+      <c r="H12">
+        <v>5</v>
+      </c>
+      <c r="I12">
+        <v>12</v>
+      </c>
+      <c r="J12">
+        <v>6</v>
+      </c>
+      <c r="K12">
+        <v>0.02</v>
+      </c>
+      <c r="L12">
+        <v>0.06</v>
+      </c>
+      <c r="M12" t="s">
         <v>28</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-      <c r="H12">
-        <v>5</v>
-      </c>
-      <c r="I12">
-        <v>7</v>
-      </c>
-      <c r="J12">
-        <v>6</v>
-      </c>
-      <c r="K12">
-        <v>0.08</v>
-      </c>
-      <c r="L12">
-        <v>0.1</v>
-      </c>
-      <c r="M12" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -1731,40 +1752,40 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="C13">
         <v>0</v>
       </c>
       <c r="D13">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="E13" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="F13" t="s">
+        <v>26</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+      <c r="H13">
+        <v>5</v>
+      </c>
+      <c r="I13">
+        <v>12</v>
+      </c>
+      <c r="J13">
+        <v>6</v>
+      </c>
+      <c r="K13">
+        <v>0.02</v>
+      </c>
+      <c r="L13">
+        <v>0.06</v>
+      </c>
+      <c r="M13" t="s">
         <v>28</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-      <c r="H13">
-        <v>5</v>
-      </c>
-      <c r="I13">
-        <v>7</v>
-      </c>
-      <c r="J13">
-        <v>6</v>
-      </c>
-      <c r="K13">
-        <v>0.08</v>
-      </c>
-      <c r="L13">
-        <v>0.1</v>
-      </c>
-      <c r="M13" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -1772,40 +1793,40 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="C14">
         <v>0</v>
       </c>
       <c r="D14">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="E14" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="F14" t="s">
+        <v>26</v>
+      </c>
+      <c r="G14">
+        <v>5</v>
+      </c>
+      <c r="H14">
+        <v>5</v>
+      </c>
+      <c r="I14">
+        <v>12</v>
+      </c>
+      <c r="J14">
+        <v>6</v>
+      </c>
+      <c r="K14">
+        <v>0.02</v>
+      </c>
+      <c r="L14">
+        <v>0.06</v>
+      </c>
+      <c r="M14" t="s">
         <v>28</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-      <c r="H14">
-        <v>5</v>
-      </c>
-      <c r="I14">
-        <v>7</v>
-      </c>
-      <c r="J14">
-        <v>6</v>
-      </c>
-      <c r="K14">
-        <v>0.08</v>
-      </c>
-      <c r="L14">
-        <v>0.1</v>
-      </c>
-      <c r="M14" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -1813,40 +1834,40 @@
         <v>13</v>
       </c>
       <c r="B15">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="E15" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="F15" t="s">
+        <v>26</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+      <c r="H15">
+        <v>5</v>
+      </c>
+      <c r="I15">
+        <v>12</v>
+      </c>
+      <c r="J15">
+        <v>6</v>
+      </c>
+      <c r="K15">
+        <v>0.02</v>
+      </c>
+      <c r="L15">
+        <v>0.06</v>
+      </c>
+      <c r="M15" t="s">
         <v>28</v>
-      </c>
-      <c r="G15">
-        <v>5</v>
-      </c>
-      <c r="H15">
-        <v>5</v>
-      </c>
-      <c r="I15">
-        <v>7</v>
-      </c>
-      <c r="J15">
-        <v>6</v>
-      </c>
-      <c r="K15">
-        <v>0.08</v>
-      </c>
-      <c r="L15">
-        <v>0.1</v>
-      </c>
-      <c r="M15" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -1854,40 +1875,40 @@
         <v>14</v>
       </c>
       <c r="B16">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="C16">
         <v>0</v>
       </c>
       <c r="D16">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="E16" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="F16" t="s">
+        <v>26</v>
+      </c>
+      <c r="G16">
+        <v>5</v>
+      </c>
+      <c r="H16">
+        <v>5</v>
+      </c>
+      <c r="I16">
+        <v>12</v>
+      </c>
+      <c r="J16">
+        <v>6</v>
+      </c>
+      <c r="K16">
+        <v>0.02</v>
+      </c>
+      <c r="L16">
+        <v>0.06</v>
+      </c>
+      <c r="M16" t="s">
         <v>28</v>
-      </c>
-      <c r="G16">
-        <v>5</v>
-      </c>
-      <c r="H16">
-        <v>5</v>
-      </c>
-      <c r="I16">
-        <v>7</v>
-      </c>
-      <c r="J16">
-        <v>6</v>
-      </c>
-      <c r="K16">
-        <v>0.08</v>
-      </c>
-      <c r="L16">
-        <v>0.1</v>
-      </c>
-      <c r="M16" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -1895,40 +1916,40 @@
         <v>15</v>
       </c>
       <c r="B17">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="C17">
         <v>0</v>
       </c>
       <c r="D17">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="E17" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="F17" t="s">
+        <v>26</v>
+      </c>
+      <c r="G17">
+        <v>5</v>
+      </c>
+      <c r="H17">
+        <v>5</v>
+      </c>
+      <c r="I17">
+        <v>12</v>
+      </c>
+      <c r="J17">
+        <v>6</v>
+      </c>
+      <c r="K17">
+        <v>0.02</v>
+      </c>
+      <c r="L17">
+        <v>0.06</v>
+      </c>
+      <c r="M17" t="s">
         <v>28</v>
-      </c>
-      <c r="G17">
-        <v>5</v>
-      </c>
-      <c r="H17">
-        <v>5</v>
-      </c>
-      <c r="I17">
-        <v>7</v>
-      </c>
-      <c r="J17">
-        <v>6</v>
-      </c>
-      <c r="K17">
-        <v>0.08</v>
-      </c>
-      <c r="L17">
-        <v>0.1</v>
-      </c>
-      <c r="M17" t="s">
-        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1951,11 +1972,11 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90EEE307-979B-4ECB-9856-D032F4306756}">
   <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="8.83984375" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="13.68359375" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="12.7890625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.26171875" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="12.83984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.3125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004">
@@ -1983,13 +2004,13 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="D2">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="E2">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -1997,16 +2018,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="D3">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="E3">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -2014,16 +2035,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="D4">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="E4">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -2031,16 +2052,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="D5">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="E5">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -2051,13 +2072,13 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="D6">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="E6">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -2068,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="C7">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="D7">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="E7">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -2082,16 +2103,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C8">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="D8">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="E8">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -2099,16 +2120,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C9">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="D9">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="E9">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -2119,13 +2140,13 @@
         <v>0</v>
       </c>
       <c r="C10">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="D10">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="E10">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -2136,13 +2157,13 @@
         <v>0</v>
       </c>
       <c r="C11">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="D11">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="E11">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -2153,13 +2174,13 @@
         <v>1</v>
       </c>
       <c r="C12">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="D12">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="E12">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -2170,13 +2191,13 @@
         <v>1</v>
       </c>
       <c r="C13">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="D13">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="E13">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -2187,13 +2208,13 @@
         <v>1</v>
       </c>
       <c r="C14">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="D14">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="E14">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -2201,16 +2222,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C15">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="D15">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="E15">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -2221,13 +2242,13 @@
         <v>0</v>
       </c>
       <c r="C16">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="D16">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="E16">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -2238,13 +2259,13 @@
         <v>0</v>
       </c>
       <c r="C17">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="D17">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="E17">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -2256,9 +2277,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31BF5B37-6521-4A27-9828-21E1EAB4E07C}">
   <dimension ref="A1:B17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="8.83984375" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="2" max="2" width="12.89453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.83984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -2409,18 +2430,16 @@
   <sheetFormatPr defaultColWidth="8.83984375" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="5.83984375" customWidth="1"/>
-    <col min="2" max="2" width="14.20703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.1015625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.20703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.15625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.9453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="14.15625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="8.15625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.47265625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="17.15625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.05078125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.3671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.3125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12.83984375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="13.15625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.62890625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.68359375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -2428,19 +2447,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>27</v>
-      </c>
       <c r="E1" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>2</v>
@@ -2469,19 +2488,19 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C2">
         <v>100</v>
       </c>
       <c r="D2">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="E2" t="s">
         <v>19</v>
       </c>
       <c r="F2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -2502,7 +2521,7 @@
         <v>0.1</v>
       </c>
       <c r="M2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -2510,19 +2529,19 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C3">
         <v>100</v>
       </c>
       <c r="D3">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="E3" t="s">
         <v>19</v>
       </c>
       <c r="F3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -2543,7 +2562,7 @@
         <v>0.1</v>
       </c>
       <c r="M3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -2551,19 +2570,19 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C4">
         <v>100</v>
       </c>
       <c r="D4">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="E4" t="s">
         <v>19</v>
       </c>
       <c r="F4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -2584,7 +2603,7 @@
         <v>0.1</v>
       </c>
       <c r="M4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -2592,19 +2611,19 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C5">
         <v>100</v>
       </c>
       <c r="D5">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="E5" t="s">
         <v>19</v>
       </c>
       <c r="F5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -2625,7 +2644,7 @@
         <v>0.1</v>
       </c>
       <c r="M5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -2633,19 +2652,19 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C6">
         <v>100</v>
       </c>
       <c r="D6">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="E6" t="s">
         <v>19</v>
       </c>
       <c r="F6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -2666,7 +2685,7 @@
         <v>0.1</v>
       </c>
       <c r="M6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -2674,19 +2693,19 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C7">
         <v>100</v>
       </c>
       <c r="D7">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="E7" t="s">
         <v>19</v>
       </c>
       <c r="F7" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -2707,7 +2726,7 @@
         <v>0.1</v>
       </c>
       <c r="M7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -2715,19 +2734,19 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C8">
         <v>100</v>
       </c>
       <c r="D8">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="E8" t="s">
         <v>19</v>
       </c>
       <c r="F8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -2748,7 +2767,7 @@
         <v>0.1</v>
       </c>
       <c r="M8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -2756,19 +2775,19 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C9">
         <v>100</v>
       </c>
       <c r="D9">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="E9" t="s">
         <v>19</v>
       </c>
       <c r="F9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -2789,7 +2808,7 @@
         <v>0.1</v>
       </c>
       <c r="M9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -2797,19 +2816,19 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C10">
         <v>100</v>
       </c>
       <c r="D10">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="E10" t="s">
         <v>19</v>
       </c>
       <c r="F10" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -2830,7 +2849,7 @@
         <v>0.1</v>
       </c>
       <c r="M10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -2838,19 +2857,19 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C11">
         <v>100</v>
       </c>
       <c r="D11">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="E11" t="s">
         <v>19</v>
       </c>
       <c r="F11" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -2871,7 +2890,7 @@
         <v>0.1</v>
       </c>
       <c r="M11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -2879,19 +2898,19 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C12">
         <v>100</v>
       </c>
       <c r="D12">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="E12" t="s">
         <v>19</v>
       </c>
       <c r="F12" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -2912,7 +2931,7 @@
         <v>0.1</v>
       </c>
       <c r="M12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -2920,19 +2939,19 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C13">
         <v>100</v>
       </c>
       <c r="D13">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="E13" t="s">
         <v>19</v>
       </c>
       <c r="F13" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -2953,7 +2972,7 @@
         <v>0.1</v>
       </c>
       <c r="M13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -2961,19 +2980,19 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14">
         <v>100</v>
       </c>
       <c r="D14">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="E14" t="s">
         <v>19</v>
       </c>
       <c r="F14" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -2994,7 +3013,7 @@
         <v>0.1</v>
       </c>
       <c r="M14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -3002,19 +3021,19 @@
         <v>13</v>
       </c>
       <c r="B15">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C15">
         <v>100</v>
       </c>
       <c r="D15">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="E15" t="s">
         <v>19</v>
       </c>
       <c r="F15" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -3035,7 +3054,7 @@
         <v>0.1</v>
       </c>
       <c r="M15" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -3043,19 +3062,19 @@
         <v>14</v>
       </c>
       <c r="B16">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C16">
         <v>100</v>
       </c>
       <c r="D16">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="E16" t="s">
         <v>19</v>
       </c>
       <c r="F16" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G16">
         <v>5</v>
@@ -3076,7 +3095,7 @@
         <v>0.1</v>
       </c>
       <c r="M16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -3084,19 +3103,19 @@
         <v>15</v>
       </c>
       <c r="B17">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C17">
         <v>100</v>
       </c>
       <c r="D17">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="E17" t="s">
         <v>19</v>
       </c>
       <c r="F17" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G17">
         <v>5</v>
@@ -3117,7 +3136,7 @@
         <v>0.1</v>
       </c>
       <c r="M17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -3140,11 +3159,11 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A9B4294-3FA5-45A6-B166-A8D0423D3D74}">
   <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="8.83984375" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="13.68359375" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="12.7890625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.26171875" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="12.83984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.3125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004">
@@ -3445,9 +3464,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6270CC91-C7EB-4578-B7FC-A30C86D3E7B4}">
   <dimension ref="A1:B17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="8.83984375" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="2" max="2" width="12.89453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.83984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3595,19 +3614,19 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A245ECA0-28EC-4A16-B4DE-14A4BDF7F5DD}">
   <dimension ref="A1:M17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="8.83984375" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="2" max="2" width="13.20703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.20703125" customWidth="1"/>
+    <col min="2" max="2" width="13.15625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.15625" customWidth="1"/>
     <col min="4" max="4" width="17.68359375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.47265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.1015625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.05078125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.3671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.15625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.3125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12.83984375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.15625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.5234375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.20703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.47265625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.15625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12.47265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3616,10 +3635,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>18</v>
@@ -3660,7 +3679,7 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D2">
         <v>40</v>
@@ -3701,7 +3720,7 @@
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D3">
         <v>40</v>
@@ -3742,7 +3761,7 @@
         <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D4">
         <v>40</v>
@@ -3783,7 +3802,7 @@
         <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D5">
         <v>40</v>
@@ -3824,7 +3843,7 @@
         <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D6">
         <v>40</v>
@@ -3865,7 +3884,7 @@
         <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D7">
         <v>40</v>
@@ -3906,7 +3925,7 @@
         <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D8">
         <v>40</v>
@@ -3947,7 +3966,7 @@
         <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D9">
         <v>40</v>
@@ -3988,7 +4007,7 @@
         <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D10">
         <v>40</v>
@@ -4029,7 +4048,7 @@
         <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D11">
         <v>40</v>
@@ -4070,7 +4089,7 @@
         <v>19</v>
       </c>
       <c r="C12" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D12">
         <v>40</v>
@@ -4111,7 +4130,7 @@
         <v>19</v>
       </c>
       <c r="C13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D13">
         <v>40</v>
@@ -4149,10 +4168,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C14" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D14">
         <v>40</v>
@@ -4190,10 +4209,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C15" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D15">
         <v>40</v>
@@ -4231,10 +4250,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C16" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D16">
         <v>40</v>
@@ -4272,10 +4291,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C17" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D17">
         <v>40</v>
@@ -4317,11 +4336,11 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E49C5A42-5AA9-4484-8593-A550BEA149B1}">
   <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="8.83984375" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="13.68359375" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="12.7890625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.26171875" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="12.83984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.3125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004">
@@ -4622,9 +4641,9 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACB49812-9D86-4204-944A-0BDF9B6E9617}">
   <dimension ref="A1:B17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="8.83984375" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="2" max="2" width="12.89453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.83984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
